--- a/samples/02_budget_2024_2025.xlsx
+++ b/samples/02_budget_2024_2025.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>400000</v>
+        <v>416000</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1750000</v>
+        <v>1820000</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1750000</v>
+        <v>1855000</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1750000</v>
+        <v>1820000</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1750000</v>
+        <v>2065000</v>
       </c>
       <c r="D37" t="inlineStr"/>
     </row>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1900000</v>
+        <v>1976000</v>
       </c>
       <c r="D40" t="inlineStr"/>
     </row>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1900000</v>
+        <v>2014000</v>
       </c>
       <c r="D43" t="inlineStr"/>
     </row>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1900000</v>
+        <v>1976000</v>
       </c>
       <c r="D46" t="inlineStr"/>
     </row>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1900000</v>
+        <v>2242000</v>
       </c>
       <c r="D49" t="inlineStr"/>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2400000</v>
+        <v>2304000</v>
       </c>
       <c r="D50" t="inlineStr"/>
     </row>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2400000</v>
+        <v>2256000</v>
       </c>
       <c r="D51" t="inlineStr"/>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2400000</v>
+        <v>2304000</v>
       </c>
       <c r="D55" t="inlineStr"/>
     </row>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2400000</v>
+        <v>2208000</v>
       </c>
       <c r="D56" t="inlineStr"/>
     </row>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2400000</v>
+        <v>2208000</v>
       </c>
       <c r="D57" t="inlineStr"/>
     </row>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2400000</v>
+        <v>2520000</v>
       </c>
       <c r="D59" t="inlineStr"/>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2400000</v>
+        <v>2640000</v>
       </c>
       <c r="D60" t="inlineStr"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2400000</v>
+        <v>2880000</v>
       </c>
       <c r="D61" t="inlineStr"/>
     </row>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2700000</v>
+        <v>2592000</v>
       </c>
       <c r="D62" t="inlineStr"/>
     </row>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2700000</v>
+        <v>2538000</v>
       </c>
       <c r="D63" t="inlineStr"/>
     </row>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2700000</v>
+        <v>2592000</v>
       </c>
       <c r="D67" t="inlineStr"/>
     </row>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2700000</v>
+        <v>2484000</v>
       </c>
       <c r="D68" t="inlineStr"/>
     </row>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2700000</v>
+        <v>2484000</v>
       </c>
       <c r="D69" t="inlineStr"/>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2700000</v>
+        <v>2835000</v>
       </c>
       <c r="D71" t="inlineStr"/>
     </row>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2700000</v>
+        <v>2970000</v>
       </c>
       <c r="D72" t="inlineStr"/>
     </row>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2700000</v>
+        <v>3240000</v>
       </c>
       <c r="D73" t="inlineStr"/>
     </row>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>300000</v>
+        <v>288000</v>
       </c>
       <c r="D74" t="inlineStr"/>
     </row>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>300000</v>
+        <v>282000</v>
       </c>
       <c r="D75" t="inlineStr"/>
     </row>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>300000</v>
+        <v>288000</v>
       </c>
       <c r="D79" t="inlineStr"/>
     </row>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="D80" t="inlineStr"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="D81" t="inlineStr"/>
     </row>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>300000</v>
+        <v>315000</v>
       </c>
       <c r="D83" t="inlineStr"/>
     </row>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="D84" t="inlineStr"/>
     </row>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="D85" t="inlineStr"/>
     </row>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>280000</v>
+        <v>269000</v>
       </c>
       <c r="D86" t="inlineStr"/>
     </row>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>280000</v>
+        <v>263000</v>
       </c>
       <c r="D87" t="inlineStr"/>
     </row>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>280000</v>
+        <v>269000</v>
       </c>
       <c r="D91" t="inlineStr"/>
     </row>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>280000</v>
+        <v>258000</v>
       </c>
       <c r="D92" t="inlineStr"/>
     </row>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>280000</v>
+        <v>258000</v>
       </c>
       <c r="D93" t="inlineStr"/>
     </row>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>280000</v>
+        <v>294000</v>
       </c>
       <c r="D95" t="inlineStr"/>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>280000</v>
+        <v>308000</v>
       </c>
       <c r="D96" t="inlineStr"/>
     </row>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>280000</v>
+        <v>336000</v>
       </c>
       <c r="D97" t="inlineStr"/>
     </row>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>320000</v>
+        <v>307000</v>
       </c>
       <c r="D98" t="inlineStr"/>
     </row>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>320000</v>
+        <v>301000</v>
       </c>
       <c r="D99" t="inlineStr"/>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>320000</v>
+        <v>307000</v>
       </c>
       <c r="D103" t="inlineStr"/>
     </row>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>320000</v>
+        <v>294000</v>
       </c>
       <c r="D104" t="inlineStr"/>
     </row>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>320000</v>
+        <v>294000</v>
       </c>
       <c r="D105" t="inlineStr"/>
     </row>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>320000</v>
+        <v>336000</v>
       </c>
       <c r="D107" t="inlineStr"/>
     </row>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>320000</v>
+        <v>352000</v>
       </c>
       <c r="D108" t="inlineStr"/>
     </row>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>320000</v>
+        <v>384000</v>
       </c>
       <c r="D109" t="inlineStr"/>
     </row>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>380000</v>
+        <v>365000</v>
       </c>
       <c r="D110" t="inlineStr"/>
     </row>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>380000</v>
+        <v>357000</v>
       </c>
       <c r="D111" t="inlineStr"/>
     </row>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>380000</v>
+        <v>365000</v>
       </c>
       <c r="D115" t="inlineStr"/>
     </row>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>380000</v>
+        <v>350000</v>
       </c>
       <c r="D116" t="inlineStr"/>
     </row>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>380000</v>
+        <v>350000</v>
       </c>
       <c r="D117" t="inlineStr"/>
     </row>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>380000</v>
+        <v>399000</v>
       </c>
       <c r="D119" t="inlineStr"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>380000</v>
+        <v>418000</v>
       </c>
       <c r="D120" t="inlineStr"/>
     </row>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>380000</v>
+        <v>456000</v>
       </c>
       <c r="D121" t="inlineStr"/>
     </row>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>100000</v>
+        <v>96000</v>
       </c>
       <c r="D122" t="inlineStr"/>
     </row>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>100000</v>
+        <v>94000</v>
       </c>
       <c r="D123" t="inlineStr"/>
     </row>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>100000</v>
+        <v>96000</v>
       </c>
       <c r="D127" t="inlineStr"/>
     </row>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>100000</v>
+        <v>92000</v>
       </c>
       <c r="D128" t="inlineStr"/>
     </row>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>100000</v>
+        <v>92000</v>
       </c>
       <c r="D129" t="inlineStr"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>100000</v>
+        <v>105000</v>
       </c>
       <c r="D131" t="inlineStr"/>
     </row>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D132" t="inlineStr"/>
     </row>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D133" t="inlineStr"/>
     </row>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>80000</v>
+        <v>77000</v>
       </c>
       <c r="D134" t="inlineStr"/>
     </row>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>80000</v>
+        <v>75000</v>
       </c>
       <c r="D135" t="inlineStr"/>
     </row>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>80000</v>
+        <v>77000</v>
       </c>
       <c r="D139" t="inlineStr"/>
     </row>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>80000</v>
+        <v>74000</v>
       </c>
       <c r="D140" t="inlineStr"/>
     </row>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>80000</v>
+        <v>74000</v>
       </c>
       <c r="D141" t="inlineStr"/>
     </row>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>80000</v>
+        <v>84000</v>
       </c>
       <c r="D143" t="inlineStr"/>
     </row>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D144" t="inlineStr"/>
     </row>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>80000</v>
+        <v>96000</v>
       </c>
       <c r="D145" t="inlineStr"/>
     </row>
